--- a/data/output/evaluasi_17.xlsx
+++ b/data/output/evaluasi_17.xlsx
@@ -7,9 +7,17 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="1709" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1705" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="1771" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="1700" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="1701" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="1702" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="1703" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="1704" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="1705" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="1706" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="1707" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="1708" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="1709" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="1771" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,6 +435,266 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>provinsi</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bengkulu</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.793553450899287</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1709</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Tengah</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.345614145788646</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1709</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Tengah</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3.226216025194785</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1709</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Tengah</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.2585064557277436</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1709</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Tengah</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.6409695339459551</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1709</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Tengah</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-2.228960639717166</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -464,57 +732,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1709</v>
+        <v>1771</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Bengkulu Tengah</t>
+          <t>Kota Bengkulu</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-72407.88306498702</v>
+        <v>0.2184417947897715</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1709</v>
+        <v>1771</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Bengkulu Tengah</t>
+          <t>Kota Bengkulu</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1.421341959864386</v>
+        <v>-1.325886638959803</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkrt_q1-25_ril vs implisit_y-on-y_pkrt_q1-25_rev</t>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -529,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,39 +834,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1705</v>
+        <v>1701</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Seluma</t>
+          <t>Kabupaten Bengkulu Selatan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2.780861774323508</v>
+        <v>2.712487125384196</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1705</v>
+        <v>1701</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Seluma</t>
+          <t>Kabupaten Bengkulu Selatan</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -607,44 +875,72 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5070096818345681</v>
+        <v>2.374448933247991</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkrt_q1-25_ril vs implisit_y-on-y_pkrt_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1705</v>
+        <v>1701</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Seluma</t>
+          <t>Kabupaten Bengkulu Selatan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.05557106002307961</v>
+        <v>-0.1053971739999371</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1701</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Selatan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-2.494050789639586</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -659,7 +955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -696,29 +992,809 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1771</v>
+        <v>1702</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Bengkulu</t>
+          <t>Kabupaten Rejang Lebong</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.497466527131243</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1702</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Rejang Lebong</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.336904442913936</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1703</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.751391028006003</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1703</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
+      <c r="D3" t="n">
+        <v>2.629602044678654</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1703</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bengkulu Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.60461225146946</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1704</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaur</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
       <c r="D2" t="n">
-        <v>0.3033237615418749</v>
+        <v>3.538086694278728</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkrt_q1-25_ril vs implisit_y-on-y_pkrt_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1704</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kaur</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-3.273919384681278</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1705</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Seluma</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>3.254358828917487</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1705</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Seluma</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-3.047683742182399</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1705</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Seluma</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.399308321141265</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1706</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Mukomuko</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>5.046986110198469</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1706</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Mukomuko</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3.947078964496924</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1706</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Mukomuko</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.4080834453561243</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1706</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Mukomuko</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-4.478263128729859</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1707</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Lebong</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.414368530601868</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1707</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Lebong</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.258830634757059</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1708</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepahiang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2.906057263514192</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1708</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepahiang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.24024423171441</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1708</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Kepahiang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-2.637425593027385</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
